--- a/converted_files/835/negotiated_discount.xlsx
+++ b/converted_files/835/negotiated_discount.xlsx
@@ -319,7 +319,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>6a68fd29aa71f5c1ede9193b</t>
+          <t>6aaac752fd84853fa5df8315</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -525,7 +525,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:BC1"/>
+  <dimension ref="A1:AZ1"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -766,40 +766,25 @@
       </c>
       <c r="AV1" s="3" t="inlineStr">
         <is>
-          <t>RemittanceDeliveryMethodReportTransmissionCode</t>
+          <t>ProviderIdentifier</t>
         </is>
       </c>
       <c r="AW1" s="3" t="inlineStr">
         <is>
-          <t>RemittanceDeliveryMethodName</t>
+          <t>FiscalPeriodDate</t>
         </is>
       </c>
       <c r="AX1" s="3" t="inlineStr">
         <is>
-          <t>RemittanceDeliveryMethodCommunicationNumber</t>
+          <t>ProviderAdjustmentReason</t>
         </is>
       </c>
       <c r="AY1" s="3" t="inlineStr">
         <is>
-          <t>ProviderIdentifier</t>
+          <t>ProviderAdjustmentReferenceIdentification</t>
         </is>
       </c>
       <c r="AZ1" s="3" t="inlineStr">
-        <is>
-          <t>FiscalPeriodDate</t>
-        </is>
-      </c>
-      <c r="BA1" s="3" t="inlineStr">
-        <is>
-          <t>ProviderAdjustmentReason</t>
-        </is>
-      </c>
-      <c r="BB1" s="3" t="inlineStr">
-        <is>
-          <t>ProviderAdjustmentReferenceIdentification</t>
-        </is>
-      </c>
-      <c r="BC1" s="3" t="inlineStr">
         <is>
           <t>ProviderAdjustmentAmount</t>
         </is>
@@ -1860,7 +1845,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>6a68fd29aa71f5c1ede91994</t>
+          <t>6aaac752fd84853fa5df8370</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -2522,7 +2507,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>6a68fd29aa71f5c1ede91994</t>
+          <t>6aaac752fd84853fa5df8370</t>
         </is>
       </c>
       <c r="B3"/>
@@ -2786,7 +2771,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>6a68fd29aa71f5c1ede91994</t>
+          <t>6aaac752fd84853fa5df8370</t>
         </is>
       </c>
       <c r="B4"/>
@@ -3050,7 +3035,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>6a68fd29aa71f5c1ede91994</t>
+          <t>6aaac752fd84853fa5df8370</t>
         </is>
       </c>
       <c r="B5"/>
@@ -3314,7 +3299,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>6a68fd29aa71f5c1ede91994</t>
+          <t>6aaac752fd84853fa5df8370</t>
         </is>
       </c>
       <c r="B6"/>

--- a/converted_files/835/negotiated_discount.xlsx
+++ b/converted_files/835/negotiated_discount.xlsx
@@ -6,9 +6,9 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Transactions" r:id="rId3" sheetId="1"/>
-    <sheet name="ProviderAdjustments" r:id="rId4" sheetId="2"/>
-    <sheet name="Service Lines" r:id="rId5" sheetId="3"/>
+    <sheet name="Remittances" r:id="rId3" sheetId="1"/>
+    <sheet name="Provider Adjustments" r:id="rId4" sheetId="2"/>
+    <sheet name="Claims and Service Lines" r:id="rId5" sheetId="3"/>
   </sheets>
 </workbook>
 </file>
@@ -319,7 +319,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>6aaac752fd84853fa5df8315</t>
+          <t>6ad90888b0eac4437b3059b5</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -1845,7 +1845,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>6aaac752fd84853fa5df8370</t>
+          <t>6ad90888b0eac4437b305a10</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -2507,7 +2507,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>6aaac752fd84853fa5df8370</t>
+          <t>6ad90888b0eac4437b305a10</t>
         </is>
       </c>
       <c r="B3"/>
@@ -2771,7 +2771,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>6aaac752fd84853fa5df8370</t>
+          <t>6ad90888b0eac4437b305a10</t>
         </is>
       </c>
       <c r="B4"/>
@@ -3035,7 +3035,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>6aaac752fd84853fa5df8370</t>
+          <t>6ad90888b0eac4437b305a10</t>
         </is>
       </c>
       <c r="B5"/>
@@ -3299,7 +3299,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>6aaac752fd84853fa5df8370</t>
+          <t>6ad90888b0eac4437b305a10</t>
         </is>
       </c>
       <c r="B6"/>
